--- a/chuangdi/数据/核算口径表.xlsx
+++ b/chuangdi/数据/核算口径表.xlsx
@@ -10,7 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="压铸铝辅材" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="铁箱辅材" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每平米收口" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="箱体" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="电源" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="支架" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安装抱箍和螺钉" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每平米收口" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,20 +420,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>本文件整理自大模组核算原表，定位是造价演算底稿中的「数量口径 + 辅材 BOM」，不是又一份模组/箱体价目。</t>
+          <t>本文件整理自大模组核算原表：辅材 BOM、每平米收口结构、箱体/电源/支架/抱箍价目。「每平米收口」样例行是历史底稿，项目报价由 Agent 按招标+规格+本表规则重算本项目收口，不是样例×面积。</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Agent 报价三件套：规格单价表（大件单价）+ 本表 BOM/收口（小件摊到每平米）+ 计价 skill（公式骨架）。</t>
+          <t>三件套：规格单价表（模组/灯珠/套件及物理箱 SKU）+ 本表（BOM、收口结构、元/㎡箱体与电源/支架/抱箍价目）+ 计价 skill。详见方案/场景演示建议口径.md、原表公式与经验配量确认.md。</t>
         </is>
       </c>
     </row>
@@ -443,21 +447,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>每平米收口：保留点间距×箱体材料行、1㎡模组数量、电源数量；包材/辅材公式引用辅材表。模组单价、箱体单价、电源单价列留空——取自规格单价表，勿在此另维护一份。</t>
+          <t>每平米收口：保留结构与对辅材/箱体/电源的公式引用；模组单价列正式稿留空（取规格单价表）。表内「1㎡模组数量」「常规电源数量」为样例/待成本确认的经验位，不作未确认的项目默认取数。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>公式骨架相对固定；BOM 明细与常数加价（如辅材公式中的 +20）由成本岗维护，改后同步 skill。</t>
+          <t>价目页「箱体」「电源」「支架」「安装抱箍和螺钉」自原表迁入；正式稿单价空/0 由成本维护。规格单价表「箱体单价」仅作物料核对，平方单价中的箱体元/㎡以本册「箱体」为准。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>招标报价用抄录面积，不依赖原屏体清单样例长宽。供应商名不转入。</t>
+          <t>不转入屏体清单样例页、压铸铝控制箱。招标用抄录面积。供应商名不转入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BOM 明细与常数加价（如辅材 +20）由成本岗维护，改后同步 skill。</t>
         </is>
       </c>
     </row>
@@ -3810,6 +3821,2988 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>箱体单价</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>箱体单价</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>配件单价</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>综合单价</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>压铸铝箱体</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <f>E3+F3</f>
+        <v/>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>不含包边</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>镀锌钢板箱体</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="G4">
+        <f>E4+F4</f>
+        <v/>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>不含包边</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>镀锌钢板箱体</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="G5">
+        <f>E5+F5</f>
+        <v/>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>含包边</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>电源单价</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>规格</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>功率因素</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>温度</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>100W/5V</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>100W/5V</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>高功率因素</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100W/5V</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>高功率因素</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>110W/3.2V+3.8V</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>高功率因素</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>110W/3.2V+3.8V</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>高功率因素</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>175W/3.2V+3.8V</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>高功率因素</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>175W/3.2V+3.8V</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>高功率因素</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>200W/5V</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>44厚款</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>200W/5V</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>高功率因素</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>200W/5V</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>高功率因素</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>175W/3.2V+3.8V</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>高功率因素</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>175W/3.2V+3.8V</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>高功率因素</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>300W/5V</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>300W/5V</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>高功率因素</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>300W/5V</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>高功率因素</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>支架单价</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>支架单价</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>螺钉配件单价</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>综合单价</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>收费大棚吊装吊架</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>平方</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>400</v>
+      </c>
+      <c r="F3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G3">
+        <f>E3+F3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>收费大棚背部支架</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>平方</t>
+        </is>
+      </c>
+      <c r="G4">
+        <f>E4+F4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>路段1米高支撑架</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>平方</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>110</v>
+      </c>
+      <c r="F5">
+        <f>安装抱箍和螺钉!L5</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>E5+F5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>路段2米高支撑架</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>平方</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>160</v>
+      </c>
+      <c r="F6">
+        <f>安装抱箍和螺钉!L6</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>E6+F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>路段1㎡支撑架</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>400</v>
+      </c>
+      <c r="F7">
+        <f>安装抱箍和螺钉!L7</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>E7+F7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>路段2㎡支撑架</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>400</v>
+      </c>
+      <c r="F8">
+        <f>安装抱箍和螺钉!L8</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>E8+F8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>路段4㎡支撑架</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>400</v>
+      </c>
+      <c r="F9">
+        <f>安装抱箍和螺钉!L9</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>E9+F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>悬臂含走道支架</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="F10">
+        <f>安装抱箍和螺钉!L9</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>E10+F10</f>
+        <v/>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3.2*1.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>悬臂含走道支架</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="F11">
+        <f>安装抱箍和螺钉!L10</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>E11+F11</f>
+        <v/>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4*2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>洞内屏2支架2节支架</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E12">
+        <f>E24</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>E35+8*10</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>E12+F12</f>
+        <v/>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>含膨胀螺栓</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>洞内屏2支架3节支架</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E13">
+        <f>E43</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>E53+8*10</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>E13+F13</f>
+        <v/>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>含膨胀螺栓</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>洞内屏3支架3节支架</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E14">
+        <f>E63</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>E73+12*10</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>E14+F14</f>
+        <v/>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>含膨胀螺栓</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>洞内侧壁1.6*3.2支架</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E15">
+        <f>400*1.6*3.2</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>1.6*3.2*3*16</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>E15+F15</f>
+        <v/>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>含膨胀螺栓</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>洞内侧壁1*2支架</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E16">
+        <f>400*2</f>
+        <v/>
+      </c>
+      <c r="F16">
+        <f>1*2*4*16</f>
+        <v/>
+      </c>
+      <c r="G16">
+        <f>E16+F16</f>
+        <v/>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>含膨胀螺栓</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>服务区</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>平方</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>600</v>
+      </c>
+      <c r="F17" t="n">
+        <v>50</v>
+      </c>
+      <c r="G17">
+        <f>E17+F17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>洞内两支架两节</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BOM层级</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>子项物料编码</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>物料名称</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>含税单价</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>价税合计</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>标准用量</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>实际数量</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>替代方式</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3000001603</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>洞内拱顶可变信息标志（双色)/P25 2R1G 200*200/CDCKB25+DN01/2500*1300*200/SGCC=1.5  蓝灰色(钣金箱体）2025-BS013</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10413.57</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10413.57</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1700000482</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>洞内吊架顶安装板/CDTPJ-AZL-C2B/280*200*295/Q235=20MM 热镀锌本色</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>167.96</v>
+      </c>
+      <c r="E22" t="n">
+        <v>335.92</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1700000107</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>洞内吊架下安装支架/CDTPJ-AZL-C4/300*200*300/槽钢+Q235 热镀锌本色</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>131.12</v>
+      </c>
+      <c r="E23" t="n">
+        <v>262.24</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2支架成本总计</t>
+        </is>
+      </c>
+      <c r="E24">
+        <f>SUM(E22:E23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>洞内两支架两节</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1600000048</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>不锈钢弹垫/M24/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1600000054</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>不锈钢平垫/M24/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1600000007</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>螺母/M24/不锈钢；A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="E29" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1600000042</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>外六角螺栓/M24*80/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1600000041</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>外六角螺栓/M18*60/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="E31" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8</v>
+      </c>
+      <c r="G31" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1600000047</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>不锈钢弹垫/M18/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8</v>
+      </c>
+      <c r="G32" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1600000053</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>不锈钢平垫/M18/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="F33" t="n">
+        <v>16</v>
+      </c>
+      <c r="G33" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1600000006</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>螺母/M18/不锈钢；A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G34" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>总计螺钉</t>
+        </is>
+      </c>
+      <c r="E35">
+        <f>SUM(E27:E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>洞内两支架三节</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BOM层级</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>子项物料编码</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>物料名称</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>含税单价</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>价税合计</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>标准用量</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>实际数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>3000001744</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>洞内拱顶可变信息标志（双色)/P25 2R1G 400*200/CDCKB25+DN01/2500*1300*200/SGCC=1.5 蓝灰色(钣金箱体）2025-S561</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10132.8</v>
+      </c>
+      <c r="E39" t="n">
+        <v>10132.8</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1700000482</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>洞内吊架顶安装板/CDTPJ-AZL-C2B/280*200*295/Q235=20MM 热镀锌本色</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>167.96</v>
+      </c>
+      <c r="E40" t="n">
+        <v>335.92</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1700000107</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>洞内吊架下安装支架/CDTPJ-AZL-C4/300*200*300/槽钢+Q235 热镀锌本色</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>131.12</v>
+      </c>
+      <c r="E41" t="n">
+        <v>262.24</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1700000106</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>洞内吊架中间调节槽钢/CDTPJ-AZL-C3/120*53*450/槽钢 热镀锌本色</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>45.799999</v>
+      </c>
+      <c r="E42" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3件套支架总计</t>
+        </is>
+      </c>
+      <c r="E43">
+        <f>SUM(E40:E42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>洞内两支架三节</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1600000041</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>外六角螺栓/M18*60/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="E45" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="F45" t="n">
+        <v>8</v>
+      </c>
+      <c r="G45" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1600000047</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>不锈钢弹垫/M18/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F46" t="n">
+        <v>8</v>
+      </c>
+      <c r="G46" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1600000053</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>不锈钢平垫/M18/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E47" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="F47" t="n">
+        <v>16</v>
+      </c>
+      <c r="G47" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1600000006</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>螺母/M18/不锈钢；A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E48" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F48" t="n">
+        <v>8</v>
+      </c>
+      <c r="G48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1600000048</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>不锈钢弹垫/M24/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1600000054</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>不锈钢平垫/M24/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E50" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="F50" t="n">
+        <v>16</v>
+      </c>
+      <c r="G50" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1600000007</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>螺母/M24/不锈钢；A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="E51" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="F51" t="n">
+        <v>16</v>
+      </c>
+      <c r="G51" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1600000042</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>外六角螺栓/M24*80/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="F52" t="n">
+        <v>8</v>
+      </c>
+      <c r="G52" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>3件套螺钉总计</t>
+        </is>
+      </c>
+      <c r="E53">
+        <f>SUM(E45:E52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>洞内三支架三节</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BOM层级</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>子项物料编码</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>物料名称</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>含税单价</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>价税合计</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>标准用量</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>实际数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>3000001744</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>洞内拱顶可变信息标志（双色)/P25 2R1G 400*200/CDCKB25+DN01/2500*1300*200/SGCC=1.5 蓝灰色(钣金箱体）2025-S561</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10132.8</v>
+      </c>
+      <c r="E59" t="n">
+        <v>10132.8</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1700000482</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>洞内吊架顶安装板/CDTPJ-AZL-C2B/280*200*295/Q235=20MM 热镀锌本色</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>167.96</v>
+      </c>
+      <c r="E60">
+        <f>D60*F60</f>
+        <v/>
+      </c>
+      <c r="F60" t="n">
+        <v>3</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1700000107</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>洞内吊架下安装支架/CDTPJ-AZL-C4/300*200*300/槽钢+Q235 热镀锌本色</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>131.12</v>
+      </c>
+      <c r="E61">
+        <f>F61*D61</f>
+        <v/>
+      </c>
+      <c r="F61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1700000106</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>洞内吊架中间调节槽钢/CDTPJ-AZL-C3/120*53*450/槽钢 热镀锌本色</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>86</v>
+      </c>
+      <c r="E62">
+        <f>D62*F62</f>
+        <v/>
+      </c>
+      <c r="F62" t="n">
+        <v>3</v>
+      </c>
+      <c r="G62" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>3件套支架总计</t>
+        </is>
+      </c>
+      <c r="E63">
+        <f>SUM(E60:E62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>洞内三支架三节</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1600000041</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>外六角螺栓/M18*60/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="E65">
+        <f>D65*F65</f>
+        <v/>
+      </c>
+      <c r="F65" t="n">
+        <v>12</v>
+      </c>
+      <c r="G65">
+        <f>F65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1600000047</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>不锈钢弹垫/M18/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E66">
+        <f>D66*F66</f>
+        <v/>
+      </c>
+      <c r="F66" t="n">
+        <v>12</v>
+      </c>
+      <c r="G66">
+        <f>F66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1600000053</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>不锈钢平垫/M18/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E67">
+        <f>D67*F67</f>
+        <v/>
+      </c>
+      <c r="F67" t="n">
+        <v>24</v>
+      </c>
+      <c r="G67">
+        <f>F67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1600000006</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>螺母/M18/不锈钢；A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E68">
+        <f>D68*F68</f>
+        <v/>
+      </c>
+      <c r="F68" t="n">
+        <v>12</v>
+      </c>
+      <c r="G68">
+        <f>F68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1600000048</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>不锈钢弹垫/M24/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E69">
+        <f>D69*F69</f>
+        <v/>
+      </c>
+      <c r="F69" t="n">
+        <v>12</v>
+      </c>
+      <c r="G69">
+        <f>F69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1600000054</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>不锈钢平垫/M24/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E70">
+        <f>D70*F70</f>
+        <v/>
+      </c>
+      <c r="F70" t="n">
+        <v>24</v>
+      </c>
+      <c r="G70">
+        <f>F70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1600000007</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>螺母/M24/不锈钢；A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="E71">
+        <f>D71*F71</f>
+        <v/>
+      </c>
+      <c r="F71" t="n">
+        <v>24</v>
+      </c>
+      <c r="G71">
+        <f>F71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1600000042</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>外六角螺栓/M24*80/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E72">
+        <f>D72*F72</f>
+        <v/>
+      </c>
+      <c r="F72" t="n">
+        <v>12</v>
+      </c>
+      <c r="G72">
+        <f>F72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>3件套螺钉总计</t>
+        </is>
+      </c>
+      <c r="E73">
+        <f>SUM(E65:E72)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>安装抱箍和螺钉单价</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>抱箍数量</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>抱箍单价</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>抱箍合计</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>抱箍数量</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>几字安装件单价</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>几字安装件合计</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>螺钉配件数量</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>螺钉配件单价</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>螺钉配件合计</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>综合价格</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>收费大棚吊装吊架</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <f>C3*D3</f>
+        <v/>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <f>G3*F3</f>
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <f>J3*I3</f>
+        <v/>
+      </c>
+      <c r="L3">
+        <f>E3+H3+K3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>收费大棚背部支架</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <f>C4*D4</f>
+        <v/>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <f>G4*F4</f>
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <f>J4*I4</f>
+        <v/>
+      </c>
+      <c r="L4">
+        <f>E4+H4+K4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>路段1米高支撑架</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <f>C5*D5</f>
+        <v/>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <f>G5*F5</f>
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <f>J5*I5</f>
+        <v/>
+      </c>
+      <c r="L5">
+        <f>E5+H5+K5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>路段2米高支撑架</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <f>C6*D6</f>
+        <v/>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <f>G6*F6</f>
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <f>J6*I6</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>E6+H6+K6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>路段1㎡支撑架</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <f>C7*D7</f>
+        <v/>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <f>G7*F7</f>
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <f>J7*I7</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>E7+H7+K7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>路段2㎡支撑架</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <f>C8*D8</f>
+        <v/>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <f>G8*F8</f>
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <f>J8*I8</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>E8+H8+K8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>悬臂含走道支架3.2*1.6</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <f>C9*D9</f>
+        <v/>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <f>G9*F9</f>
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <f>J9*I9</f>
+        <v/>
+      </c>
+      <c r="L9">
+        <f>E9+H9+K9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>悬臂含走道支架4*2</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <f>C10*D10</f>
+        <v/>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <f>G10*F10</f>
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <f>J10*I10</f>
+        <v/>
+      </c>
+      <c r="L10">
+        <f>E10+H10+K10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>洞内屏2支架2节支架</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <f>C11*D11</f>
+        <v/>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <f>G11*F11</f>
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <f>J11*I11</f>
+        <v/>
+      </c>
+      <c r="L11">
+        <f>E11+H11+K11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>洞内屏2支架3节支架</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <f>C12*D12</f>
+        <v/>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <f>G12*F12</f>
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <f>J12*I12</f>
+        <v/>
+      </c>
+      <c r="L12">
+        <f>E12+H12+K12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>洞内屏3支架3节支架</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <f>C13*D13</f>
+        <v/>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <f>G13*F13</f>
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <f>J13*I13</f>
+        <v/>
+      </c>
+      <c r="L13">
+        <f>E13+H13+K13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>洞内侧壁1.6*3.2支架</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <f>C14*D14</f>
+        <v/>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <f>G13</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>G14*F14</f>
+        <v/>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <f>J13</f>
+        <v/>
+      </c>
+      <c r="K14">
+        <f>J14*I14</f>
+        <v/>
+      </c>
+      <c r="L14">
+        <f>E14+H14+K14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>洞内侧壁1*2支架</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <f>C15*D15</f>
+        <v/>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <f>G14</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>G15*F15</f>
+        <v/>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <f>J14</f>
+        <v/>
+      </c>
+      <c r="K15">
+        <f>J15*I15</f>
+        <v/>
+      </c>
+      <c r="L15">
+        <f>E15+H15+K15</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3936,9 +6929,17 @@
         <f>E3*F3</f>
         <v/>
       </c>
+      <c r="H3">
+        <f>箱体!G3</f>
+        <v/>
+      </c>
       <c r="I3" t="n">
         <v>2</v>
       </c>
+      <c r="J3">
+        <f>电源!G11</f>
+        <v/>
+      </c>
       <c r="K3">
         <f>J3*I3</f>
         <v/>
@@ -3957,7 +6958,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -4019,7 +7020,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -4056,6 +7057,10 @@
         <f>E5*F5</f>
         <v/>
       </c>
+      <c r="H5">
+        <f>箱体!G5</f>
+        <v/>
+      </c>
       <c r="I5" t="n">
         <v>2</v>
       </c>
@@ -4081,7 +7086,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -4147,7 +7152,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -4281,6 +7286,10 @@
       <c r="I9" t="n">
         <v>2</v>
       </c>
+      <c r="J9">
+        <f>电源!G10</f>
+        <v/>
+      </c>
       <c r="K9">
         <f>J9*I9</f>
         <v/>
@@ -4307,7 +7316,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -4368,7 +7377,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -4429,7 +7438,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -4491,7 +7500,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -4566,7 +7575,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -4631,7 +7640,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -4696,7 +7705,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -4762,7 +7771,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -4896,6 +7905,10 @@
       <c r="I19" t="n">
         <v>2</v>
       </c>
+      <c r="J19">
+        <f>电源!G10</f>
+        <v/>
+      </c>
       <c r="K19">
         <f>J19*I19</f>
         <v/>
@@ -4922,7 +7935,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -4984,7 +7997,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -5046,7 +8059,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -5122,7 +8135,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -5188,7 +8201,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -5254,7 +8267,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -5389,6 +8402,10 @@
         <f>I3</f>
         <v/>
       </c>
+      <c r="J27">
+        <f>电源!G10</f>
+        <v/>
+      </c>
       <c r="K27">
         <f>K3</f>
         <v/>
@@ -5415,7 +8432,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -5477,7 +8494,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -5539,7 +8556,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -5601,7 +8618,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -5663,7 +8680,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -5708,6 +8725,10 @@
         <f>I5</f>
         <v/>
       </c>
+      <c r="J32">
+        <f>电源!G10</f>
+        <v/>
+      </c>
       <c r="K32">
         <f>K5</f>
         <v/>
@@ -5734,7 +8755,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -5800,7 +8821,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -5866,7 +8887,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -5932,7 +8953,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -5998,7 +9019,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -6133,6 +9154,10 @@
         <f>I3</f>
         <v/>
       </c>
+      <c r="J39">
+        <f>电源!G10</f>
+        <v/>
+      </c>
       <c r="K39">
         <f>K3</f>
         <v/>
@@ -6159,7 +9184,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -6221,7 +9246,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -6283,7 +9308,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -6345,7 +9370,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -6407,7 +9432,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -6469,7 +9494,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -6514,6 +9539,10 @@
         <f>I5</f>
         <v/>
       </c>
+      <c r="J45">
+        <f>电源!G10</f>
+        <v/>
+      </c>
       <c r="K45">
         <f>K5</f>
         <v/>
@@ -6540,7 +9569,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -6606,7 +9635,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -6672,7 +9701,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -6738,7 +9767,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -6804,7 +9833,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>
@@ -6870,7 +9899,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>大件单价见规格单价表</t>
+          <t>模组单价见规格单价表；箱体/电源见本册价目</t>
         </is>
       </c>
     </row>

--- a/chuangdi/数据/核算口径表.xlsx
+++ b/chuangdi/数据/核算口径表.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="电源" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="支架" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安装抱箍和螺钉" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每平米收口" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控制箱" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每平米收口" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,14 +427,14 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>本文件整理自大模组核算原表：辅材 BOM、每平米收口结构、箱体/电源/支架/抱箍价目。「每平米收口」样例行是历史底稿，项目报价由 Agent 按招标+规格+本表规则重算本项目收口，不是样例×面积。</t>
+          <t>本文件整理自大模组核算原表：辅材 BOM、每平米收口结构、箱体/电源/支架/抱箍/控制箱价目。「每平米收口」样例行是历史底稿，项目报价由 Agent 按招标+规格+本表规则重算本项目收口，不是样例×面积。</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>三件套：规格单价表（模组/灯珠/套件及物理箱 SKU）+ 本表（BOM、收口结构、元/㎡箱体与电源/支架/抱箍价目）+ 计价 skill。详见方案/场景演示建议口径.md、原表公式与经验配量确认.md。</t>
+          <t>三件套：规格单价表（模组/灯珠/套件及物理箱 SKU）+ 本表（BOM、收口结构、元/㎡箱体与电源/支架/抱箍/控制箱价目）+ 计价 skill。详见方案/场景演示建议口径.md、原表公式与经验配量确认.md。</t>
         </is>
       </c>
     </row>
@@ -454,14 +455,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>价目页「箱体」「电源」「支架」「安装抱箍和螺钉」自原表迁入；正式稿单价空/0 由成本维护。规格单价表「箱体单价」仅作物料核对，平方单价中的箱体元/㎡以本册「箱体」为准。</t>
+          <t>价目页「箱体」「电源」「支架」「安装抱箍和螺钉」「控制箱」自原表迁入；正式稿单价空/0 由成本维护。规格单价表「箱体单价」仅作物料核对，平方单价中的箱体元/㎡以本册「箱体」为准。报价单「控制系统」取本册「控制箱」汇总（每套），形态加价见报价单 skill。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>不转入屏体清单样例页、压铸铝控制箱。招标用抄录面积。供应商名不转入。</t>
+          <t>不转入屏体清单样例页。招标用抄录面积。供应商名不转入。</t>
         </is>
       </c>
     </row>
@@ -6803,6 +6804,1064 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>BOM层级</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>子项物料编码</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>物料名称</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>含税单价</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3000001386</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>可变信息标志控制箱（单相含控制卡--无信号防雷版）/KXB-10P-A1-KZX+KZ03/400*610*140/SGCC=1.2 户外7035</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>..2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2300001283</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>可变信息标志控制箱（单相含控制卡-无信号防雷版）/KXB-10P-A1-KZX+KZ03/400*610*140/SGCC=1.2 户外7035 裸机</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2200000649</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>服务区情报板单相控制箱（背抱安装）箱体/KXB-KZ03D-D1/400*610*140/SGCC=1.2 户外7035</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1000000932</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>多媒体播放盒/GX30T</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1500000042</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>开关电源/LM25-23B05/5V/5A 25W/效率88%/工作温度范围：-30℃to +70℃/VEN00112</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1700000010</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>单相电源防雷器/CD-D/AC20-2（丝印创迪LOGO）/VEN00054</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1900000039</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>光探头/ALP050-1.5M-P/CON4-2.54插头</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1000000515</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>空开/DZ47SC63(63A,1P)/N</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1000000464</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>空开/DZ47sN1C32(32A,1P)/N</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1300000116</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AC30模数化插座/250V/10-16A/3孔</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1600000102</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>过线圈/PG29/尼龙/白色</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1000000480</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>空开背条/L=1000*35*7.5mm/C45导轨，1mm厚，国标</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1300000120</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>接线端子固定卡/E-UK</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1300000153</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10孔桥型接线排/8*12地排/110.8*31.8*12.5mm/绿色</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1300000154</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>10孔桥型接线排/8*12零排/110.8*31.8*12.5mm/蓝色</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1600000063</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3合1螺钉/M4*8/碳钢/镀白锌</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1600000027</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>圆头十字螺钉/M4*8/碳钢/镀白锌</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1600000064</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3合1螺钉/M4×16/碳钢/镀白锌</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1600000100</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3合1螺钉/M3*6/碳钢/包黑色</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1600000004</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>螺母/M6/碳钢/镀白锌</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1600000043</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>不锈钢弹垫/M6/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1600000049</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>不锈钢平垫/M6/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1400000142</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>一拖一5V单元板电源线/主线长0.5m 分支线长0.3m  接线叉SNB2-4 /分支线BVR铜软0.75mm² 主线国标BVR铜软2.5mm²</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1700003108</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>RJ45网口防尘塞/硅胶 黑色</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1400000060</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>铜芯聚氯乙烯绝缘阻燃软电线/ZR BVR1*1.5mm²电压450-750V/红色</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1400000059</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>铜芯聚氯乙烯绝缘阻燃软电线/ZR BVR1*1.5mm²电压450-750V/黑色</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1400000061</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>铜芯聚氯乙烯绝缘阻燃软电线/ZR BVR1*1.5mm²电压450-750V/黄绿色</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1400000063</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>铜芯聚氯乙烯绝缘阻燃软电线/ZR BVR1*1.5mm²电压450-750V/蓝色</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1400000065</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>铜芯聚氯乙烯绝缘阻燃软电线/ZR BVR1*1.5mm²电压450-750V/棕色</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1400000056</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>铜芯聚氯乙烯绝缘软电缆/BVR1*2.5mm²电压450-750V/蓝色</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1400000058</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>铜芯聚氯乙烯绝缘软电缆/BVR1*2.5mm²电压450-750V/棕色</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1400000054</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>铜芯聚氯乙烯绝缘软电缆/BVR1*2.5mm²电压450-750V/黄绿色</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1400000093</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>铜芯聚氯乙烯绝缘软电缆/BVR1*4mm²电压450-750V/棕色</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1300000129</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>冷压接线端子/SNB2-3/国标紫铜U型/16*5.7*0.8mm</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1300000126</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>冷压接线端子/C45-2.5/插片形DZ47国标紫铜/13*4.8*0.7mm</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1300000151</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>冷压接线端子/C45-6/插片形DZ47国标紫铜/13*4.8*0.7mm</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1300000128</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>冷压接线端子/RNB2-6/国标紫铜O型/21.7*12*0.8mm</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1300000127</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>冷压接线端子/RNB2-4/国标紫铜O型/14.4*6.6*0.8mm</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1700002806</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>尼龙扎带/3*150mm/黑色</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1800000465</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>重庆创迪LOGO图样/CD-LG-CDKJ</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1800000005</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>亚银标签纸/50*125</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1800000012</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>合格证不干胶贴/φ25</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1800000967</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>可变信息标志控制箱单相含控制卡-无信号防雷版使用说明书</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1800000968</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>可变信息标志单相洞外控制箱产品无信号防雷版接线示意图/150 *210 /A4光面黄底不干胶标签贴纸</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1800000109</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>纸箱/CDTPJ-ZXL-D17/内670*410*150外685*425*165/ 5层瓦楞 本色</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>..2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1700000384</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>控制箱背抱 几字连接板/KXB-KZ03-A5/140*40*33/SGCC=3 户外7035</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>..2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1600000036</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>外六角螺栓/M10*30/不锈钢/本色</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>..2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1600000044</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>不锈钢弹垫/M10/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>..2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1600000050</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>不锈钢平垫/M10/不锈钢 A2-70/本色</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1700003261</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PA尼龙波纹管（闭口）/AD34.5内径29mm外径34.5mm PA6尼龙/工作温度-40℃-100℃/黑色</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>总计辅材和箱体10平方</t>
+        </is>
+      </c>
+      <c r="E52">
+        <f>SUM(E4:E51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
